--- a/backtest_runs/20260410_193731/by_symbol/MSCL/MSCL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/MSCL/MSCL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>-9322.239999999996</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>90677.76000000001</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>98980.37999999999</v>
@@ -955,7 +955,7 @@
         <v>-582.6400000000006</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>99198.87</v>
@@ -1277,7 +1277,7 @@
         <v>-12745.25</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>116241.09</v>
@@ -1323,7 +1323,7 @@
         <v>-946.7899999999928</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>115294.3</v>
@@ -1415,7 +1415,7 @@
         <v>-4369.80000000001</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>113327.89</v>
@@ -1507,7 +1507,7 @@
         <v>-1092.44999999999</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>119591.27</v>
@@ -1553,7 +1553,7 @@
         <v>-4733.950000000003</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>114857.32</v>
@@ -1645,7 +1645,7 @@
         <v>-5243.760000000017</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>118498.82</v>
